--- a/output/topology_excel/9722.xlsx
+++ b/output/topology_excel/9722.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,57 +490,75 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>43611</v>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1275</v>
+        <v>119321</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>85</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>114732</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>235</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3660</v>
+        <v>30020</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>77</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -533,52 +566,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>115429</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1001</v>
+        <v>28440</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>75</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>238008</v>
+      </c>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2054</v>
+        <v>114732</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>88</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -591,898 +642,1177 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>115429</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1050</v>
+        <v>238008</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>746570</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>158</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2212</v>
+        <v>29920</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>86</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>119321</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1144</v>
+        <v>29920</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>88</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>119321</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>234</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11231</v>
+        <v>179269</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>94</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1204</v>
+        <v>193917</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>84</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>234</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11517</v>
+        <v>46740</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>87</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>238008</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>158924</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>89</v>
+      </c>
+      <c r="J12" t="n">
         <v>13</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>46740</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>187</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2431</v>
+        <v>158924</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>77</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>746570</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>179269</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
         <v>13</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1320</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>179269</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>28536</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>87</v>
+      </c>
+      <c r="J15" t="n">
         <v>13</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>187</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>746570</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1410</v>
+        <v>60450</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>97</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
-      </c>
-      <c r="D17" t="inlineStr">
+        <v>158924</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F17" t="n">
-        <v>316</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7750</v>
+        <v>100170</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>79</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>746570</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1092</v>
+        <v>43611</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>218</v>
+      </c>
+      <c r="J18" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>746570</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>349</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8573</v>
+        <v>119321</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>194</v>
+      </c>
+      <c r="J19" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" t="inlineStr">
+        <v>746570</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1131</v>
+        <v>29920</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>187</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>746570</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>285</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3705</v>
+        <v>179269</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>219</v>
+      </c>
+      <c r="J21" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>746570</v>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>16</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1157</v>
+        <v>60450</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>325</v>
+      </c>
+      <c r="J22" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>5890</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>108</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1404</v>
+        <v>115429</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>185</v>
+      </c>
+      <c r="J23" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>115429</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1078</v>
+        <v>6460</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>38</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
-      </c>
-      <c r="D25" t="inlineStr">
+        <v>115429</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1300</v>
+        <v>28440</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>158</v>
+      </c>
+      <c r="J25" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>115429</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>234</v>
-      </c>
-      <c r="G26" t="n">
-        <v>9100</v>
+        <v>238008</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>195</v>
+      </c>
+      <c r="J26" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>115429</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1131</v>
+        <v>193917</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>305</v>
+      </c>
+      <c r="J27" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>6460</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>355</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4615</v>
+        <v>238008</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>38</v>
+      </c>
+      <c r="J28" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>6460</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1455</v>
+        <v>28440</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>163</v>
+      </c>
+      <c r="J29" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>505</v>
-      </c>
-      <c r="G30" t="n">
-        <v>7575</v>
+        <v>6498</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>38</v>
+      </c>
+      <c r="J30" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
-      </c>
-      <c r="D31" t="inlineStr">
+        <v>238008</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1106</v>
+        <v>28440</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>194</v>
+      </c>
+      <c r="J31" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>218</v>
-      </c>
-      <c r="G32" t="n">
-        <v>4796</v>
+        <v>30020</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>203</v>
+      </c>
+      <c r="J32" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>23</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4536</v>
+        <v>114732</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>196</v>
+      </c>
+      <c r="J33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D34" t="n">
+        <v>14</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>193</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5015</v>
+        <v>193917</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>349</v>
+      </c>
+      <c r="J34" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>38</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1292</v>
+        <v>46740</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>285</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>238008</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>305</v>
-      </c>
-      <c r="G36" t="n">
-        <v>9082</v>
+        <v>158924</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>108</v>
+      </c>
+      <c r="J36" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1490,173 +1820,227 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>6498</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F37" t="n">
+        <v>114732</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>38</v>
       </c>
-      <c r="G37" t="n">
-        <v>1178</v>
+      <c r="J37" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>6498</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>38</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1216</v>
+        <v>30020</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>171</v>
+      </c>
+      <c r="J38" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>114732</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>158</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2212</v>
+        <v>6006</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>187</v>
+      </c>
+      <c r="J39" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C40" t="n">
+        <v>114732</v>
+      </c>
+      <c r="D40" t="n">
         <v>12</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F40" t="n">
+        <v>30020</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>158</v>
       </c>
-      <c r="G40" t="n">
-        <v>2054</v>
+      <c r="J40" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>114732</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2674</v>
+        <v>158924</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>297</v>
+      </c>
+      <c r="J41" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>21</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>43611</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
-      </c>
-      <c r="G42" t="n">
-        <v>5642</v>
+        <v>119321</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>228</v>
+      </c>
+      <c r="J42" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1664,110 +2048,146 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>43611</v>
+      </c>
+      <c r="D43" t="n">
+        <v>13</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>38</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1216</v>
+        <v>29920</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>151</v>
+      </c>
+      <c r="J43" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>119321</v>
+      </c>
+      <c r="D44" t="n">
+        <v>13</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>193</v>
-      </c>
-      <c r="G44" t="n">
-        <v>4983</v>
+        <v>29920</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>187</v>
+      </c>
+      <c r="J44" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>119321</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>297</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3861</v>
+        <v>179269</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>316</v>
+      </c>
+      <c r="J45" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>14</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>29920</v>
+      </c>
+      <c r="D46" t="n">
+        <v>17</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2835</v>
+        <v>179269</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>160</v>
+      </c>
+      <c r="J46" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -1780,23 +2200,32 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>193917</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>165</v>
-      </c>
-      <c r="G47" t="n">
-        <v>7447</v>
+        <v>46740</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>164</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -1809,23 +2238,32 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>193917</v>
+      </c>
+      <c r="D48" t="n">
         <v>18</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F48" t="n">
-        <v>231</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3234</v>
+        <v>100170</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>245</v>
+      </c>
+      <c r="J48" t="n">
+        <v>203</v>
       </c>
     </row>
     <row r="49">
@@ -1838,23 +2276,32 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>193917</v>
+      </c>
+      <c r="D49" t="n">
         <v>23</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F49" t="n">
-        <v>191</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4926</v>
+        <v>5814</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>186</v>
+      </c>
+      <c r="J49" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="50">
@@ -1867,23 +2314,32 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>193917</v>
+      </c>
+      <c r="D50" t="n">
+        <v>21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
-      </c>
-      <c r="G50" t="n">
-        <v>19435</v>
+        <v>30303</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>145</v>
+      </c>
+      <c r="J50" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="51">
@@ -1896,52 +2352,70 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>46740</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>285</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3990</v>
+        <v>158924</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>164</v>
+      </c>
+      <c r="J51" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>46740</v>
+      </c>
+      <c r="D52" t="n">
+        <v>18</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>193</v>
-      </c>
-      <c r="G52" t="n">
-        <v>4829</v>
+        <v>100170</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>285</v>
+      </c>
+      <c r="J52" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -1954,81 +2428,108 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>21</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>158924</v>
+      </c>
+      <c r="D53" t="n">
+        <v>18</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>39</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1365</v>
+        <v>100170</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>189</v>
+      </c>
+      <c r="J53" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>158924</v>
+      </c>
+      <c r="D54" t="n">
+        <v>21</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>160</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2880</v>
+        <v>30303</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>142</v>
+      </c>
+      <c r="J54" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>158924</v>
+      </c>
+      <c r="D55" t="n">
+        <v>22</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>17</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F55" t="n">
-        <v>15</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3375</v>
+        <v>6006</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>187</v>
+      </c>
+      <c r="J55" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="56">
@@ -2041,23 +2542,108 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>179269</v>
+      </c>
+      <c r="D56" t="n">
+        <v>19</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>28536</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>245</v>
+      </c>
+      <c r="J56" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>17</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>179269</v>
+      </c>
+      <c r="D57" t="n">
         <v>20</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
+        <v>60450</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
         <v>195</v>
       </c>
-      <c r="G56" t="n">
-        <v>2535</v>
+      <c r="J57" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>18</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>100170</v>
+      </c>
+      <c r="D58" t="n">
+        <v>21</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>30303</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>530</v>
+      </c>
+      <c r="J58" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9722.xlsx
+++ b/output/topology_excel/9722.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -961,7 +961,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1139,7 +1139,7 @@
         <v>746570</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>119321</v>
+        <v>29920</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J19" t="n">
-        <v>190</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1177,15 +1177,15 @@
         <v>746570</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29920</v>
+        <v>179269</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="J20" t="n">
         <v>13</v>
@@ -1215,15 +1215,15 @@
         <v>746570</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>179269</v>
+        <v>60450</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1234,34 +1234,34 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="J21" t="n">
-        <v>104</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>746570</v>
+        <v>5890</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>60450</v>
+        <v>115429</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1272,34 +1272,34 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>325</v>
+        <v>185</v>
       </c>
       <c r="J22" t="n">
-        <v>210</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>115429</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>5890</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="F23" t="n">
-        <v>115429</v>
+        <v>6460</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="J23" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -1329,15 +1329,15 @@
         <v>115429</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6460</v>
+        <v>28440</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="J24" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1367,15 +1367,15 @@
         <v>115429</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>28440</v>
+        <v>238008</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="J25" t="n">
         <v>14</v>
@@ -1405,15 +1405,15 @@
         <v>115429</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>238008</v>
+        <v>193917</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1424,34 +1424,34 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>195</v>
+        <v>305</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>115429</v>
+        <v>6460</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>193917</v>
+        <v>238008</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>305</v>
+        <v>38</v>
       </c>
       <c r="J27" t="n">
-        <v>132</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -1481,15 +1481,15 @@
         <v>6460</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>238008</v>
+        <v>28440</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1500,34 +1500,34 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>38</v>
+        <v>163</v>
       </c>
       <c r="J28" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>238008</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>6460</v>
-      </c>
-      <c r="D29" t="n">
-        <v>11</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
       <c r="F29" t="n">
-        <v>28440</v>
+        <v>6498</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="J29" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1557,15 +1557,15 @@
         <v>238008</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6498</v>
+        <v>28440</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="J30" t="n">
-        <v>32</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31">
@@ -1595,7 +1595,7 @@
         <v>238008</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>28440</v>
+        <v>30020</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="J31" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32">
@@ -1633,15 +1633,15 @@
         <v>238008</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>30020</v>
+        <v>114732</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J32" t="n">
-        <v>171</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -1671,7 +1671,7 @@
         <v>238008</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>114732</v>
+        <v>193917</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>196</v>
+        <v>349</v>
       </c>
       <c r="J33" t="n">
         <v>13</v>
@@ -1709,15 +1709,15 @@
         <v>238008</v>
       </c>
       <c r="D34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>193917</v>
+        <v>46740</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="J34" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
@@ -1747,15 +1747,15 @@
         <v>238008</v>
       </c>
       <c r="D35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>46740</v>
+        <v>158924</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="J35" t="n">
         <v>13</v>
@@ -1774,18 +1774,18 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>238008</v>
+        <v>6498</v>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>158924</v>
+        <v>114732</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="J36" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
@@ -1823,15 +1823,15 @@
         <v>6498</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>114732</v>
+        <v>30020</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,34 +1842,34 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="J37" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>114732</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>6498</v>
-      </c>
-      <c r="D38" t="n">
-        <v>12</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
       <c r="F38" t="n">
-        <v>30020</v>
+        <v>6006</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="J38" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39">
@@ -1899,15 +1899,15 @@
         <v>114732</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6006</v>
+        <v>30020</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="J39" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -1937,15 +1937,15 @@
         <v>114732</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>30020</v>
+        <v>158924</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="J40" t="n">
         <v>13</v>
@@ -1964,26 +1964,26 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>114732</v>
+        <v>43611</v>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>158924</v>
+        <v>119321</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="J41" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
@@ -2013,7 +2013,7 @@
         <v>43611</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>119321</v>
+        <v>29920</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2032,23 +2032,23 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>228</v>
+        <v>151</v>
       </c>
       <c r="J42" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>43611</v>
+        <v>119321</v>
       </c>
       <c r="D43" t="n">
         <v>13</v>
@@ -2070,10 +2070,10 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -2089,15 +2089,15 @@
         <v>119321</v>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>29920</v>
+        <v>179269</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2108,15 +2108,15 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>187</v>
+        <v>316</v>
       </c>
       <c r="J44" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>119321</v>
+        <v>29920</v>
       </c>
       <c r="D45" t="n">
         <v>17</v>
@@ -2146,34 +2146,34 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>316</v>
+        <v>160</v>
       </c>
       <c r="J45" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>193917</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>29920</v>
-      </c>
-      <c r="D46" t="n">
-        <v>17</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
       <c r="F46" t="n">
-        <v>179269</v>
+        <v>46740</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J46" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -2203,15 +2203,15 @@
         <v>193917</v>
       </c>
       <c r="D47" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>46740</v>
+        <v>100170</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2222,10 +2222,10 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48">
@@ -2241,15 +2241,15 @@
         <v>193917</v>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100170</v>
+        <v>5814</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="J48" t="n">
-        <v>203</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
@@ -2279,7 +2279,7 @@
         <v>193917</v>
       </c>
       <c r="D49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>5814</v>
+        <v>30303</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="J49" t="n">
         <v>62</v>
@@ -2306,40 +2306,40 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
+        <v>15</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>46740</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>158924</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>164</v>
+      </c>
+      <c r="J50" t="n">
         <v>14</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>193917</v>
-      </c>
-      <c r="D50" t="n">
-        <v>21</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>30303</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>145</v>
-      </c>
-      <c r="J50" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="51">
@@ -2355,15 +2355,15 @@
         <v>46740</v>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>158924</v>
+        <v>100170</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="J51" t="n">
         <v>14</v>
@@ -2382,15 +2382,15 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>46740</v>
+        <v>158924</v>
       </c>
       <c r="D52" t="n">
         <v>18</v>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="J52" t="n">
         <v>14</v>
@@ -2431,15 +2431,15 @@
         <v>158924</v>
       </c>
       <c r="D53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100170</v>
+        <v>30303</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2450,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -2469,7 +2469,7 @@
         <v>158924</v>
       </c>
       <c r="D54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>30303</v>
+        <v>6006</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="J54" t="n">
         <v>62</v>
@@ -2496,18 +2496,18 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>158924</v>
+        <v>179269</v>
       </c>
       <c r="D55" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6006</v>
+        <v>28536</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="J55" t="n">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56">
@@ -2545,15 +2545,15 @@
         <v>179269</v>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>28536</v>
+        <v>60450</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2564,15 +2564,15 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>245</v>
+        <v>195</v>
       </c>
       <c r="J56" t="n">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2580,18 +2580,18 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>179269</v>
+        <v>100170</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>60450</v>
+        <v>30303</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2602,47 +2602,9 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>195</v>
+        <v>530</v>
       </c>
       <c r="J57" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>18</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>100170</v>
-      </c>
-      <c r="D58" t="n">
-        <v>21</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>30303</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>530</v>
-      </c>
-      <c r="J58" t="n">
         <v>23</v>
       </c>
     </row>

--- a/output/topology_excel/9722.xlsx
+++ b/output/topology_excel/9722.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,32 +806,32 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>187</v>
+        <v>415</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>325</v>
+        <v>195</v>
       </c>
       <c r="F21" t="n">
-        <v>210</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -993,29 +993,29 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>158</v>
+      </c>
+      <c r="F26" t="n">
         <v>14</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>305</v>
-      </c>
-      <c r="F26" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>163</v>
+        <v>305</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F30" t="n">
-        <v>172</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="F31" t="n">
-        <v>171</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="F33" t="n">
         <v>13</v>
@@ -1169,7 +1169,7 @@
         <v>5</v>
       </c>
       <c r="B34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="F34" t="n">
         <v>13</v>
@@ -1191,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>38</v>
+        <v>189</v>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="F38" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="F39" t="n">
         <v>13</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="F41" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B42" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1381,15 +1381,15 @@
         <v>187</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B44" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>316</v>
+        <v>228</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>164</v>
+        <v>316</v>
       </c>
       <c r="F46" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B47" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>245</v>
+        <v>151</v>
       </c>
       <c r="F47" t="n">
-        <v>203</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B48" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,18 +1488,18 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F48" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B49" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>145</v>
+        <v>285</v>
       </c>
       <c r="F49" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" t="n">
         <v>15</v>
-      </c>
-      <c r="B50" t="n">
-        <v>16</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="F53" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B54" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F54" t="n">
-        <v>62</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B55" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,18 +1642,18 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="F55" t="n">
-        <v>136</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="F56" t="n">
         <v>13</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B57" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,10 +1686,362 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
+        <v>184</v>
+      </c>
+      <c r="F57" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>11</v>
+      </c>
+      <c r="B58" t="n">
+        <v>23</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>22</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>11</v>
+      </c>
+      <c r="B59" t="n">
+        <v>12</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>310</v>
+      </c>
+      <c r="F59" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>12</v>
+      </c>
+      <c r="B60" t="n">
+        <v>23</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>195</v>
+      </c>
+      <c r="F60" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>13</v>
+      </c>
+      <c r="B61" t="n">
+        <v>19</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>163</v>
+      </c>
+      <c r="F61" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>14</v>
+      </c>
+      <c r="B62" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>171</v>
+      </c>
+      <c r="F62" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>15</v>
+      </c>
+      <c r="B63" t="n">
+        <v>17</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>231</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>16</v>
+      </c>
+      <c r="B64" t="n">
+        <v>23</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>365</v>
+      </c>
+      <c r="F64" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>16</v>
+      </c>
+      <c r="B65" t="n">
+        <v>24</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>123</v>
+      </c>
+      <c r="F65" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>17</v>
+      </c>
+      <c r="B66" t="n">
+        <v>25</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
         <v>530</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F66" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>23</v>
+      </c>
+      <c r="B67" t="n">
+        <v>24</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>232</v>
+      </c>
+      <c r="F67" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>106</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>162</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" t="n">
+        <v>11</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>310</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="n">
+        <v>11</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>115</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5</v>
+      </c>
+      <c r="B72" t="n">
+        <v>15</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>56</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>16</v>
+      </c>
+      <c r="B73" t="n">
+        <v>23</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>185</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9722.xlsx
+++ b/output/topology_excel/9722.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>15</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>14</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>15</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>15</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>13</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>13</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>14</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>14</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>13</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>15</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>14</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,14 +891,20 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>415</v>
+        <v>115</v>
       </c>
       <c r="F19" t="n">
         <v>18</v>
       </c>
+      <c r="G19" t="n">
+        <v>256</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -869,14 +919,20 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>218</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
         <v>54</v>
       </c>
+      <c r="G20" t="n">
+        <v>42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +955,8 @@
       <c r="F21" t="n">
         <v>15</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +979,8 @@
       <c r="F22" t="n">
         <v>22</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1003,8 @@
       <c r="F23" t="n">
         <v>13</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -957,13 +1019,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="F24" t="n">
-        <v>63</v>
+        <v>30</v>
+      </c>
+      <c r="G24" t="n">
+        <v>155</v>
+      </c>
+      <c r="H24" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -987,6 +1055,8 @@
       <c r="F25" t="n">
         <v>34</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1079,8 @@
       <c r="F26" t="n">
         <v>14</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1103,8 @@
       <c r="F27" t="n">
         <v>14</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1045,12 +1119,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="F28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G28" t="n">
+        <v>42</v>
+      </c>
+      <c r="H28" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1075,6 +1155,8 @@
       <c r="F29" t="n">
         <v>32</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1089,13 +1171,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n">
-        <v>63</v>
+        <v>33</v>
+      </c>
+      <c r="G30" t="n">
+        <v>154</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -1119,6 +1207,8 @@
       <c r="F31" t="n">
         <v>13</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1231,8 @@
       <c r="F32" t="n">
         <v>13</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1255,8 @@
       <c r="F33" t="n">
         <v>13</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1279,8 @@
       <c r="F34" t="n">
         <v>13</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1199,12 +1295,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="F35" t="n">
+        <v>14</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1229,6 +1331,8 @@
       <c r="F36" t="n">
         <v>14</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1243,13 +1347,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="F37" t="n">
-        <v>62</v>
+        <v>24</v>
+      </c>
+      <c r="G37" t="n">
+        <v>38</v>
+      </c>
+      <c r="H37" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -1265,13 +1375,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="F38" t="n">
-        <v>62</v>
+        <v>23</v>
+      </c>
+      <c r="G38" t="n">
+        <v>39</v>
+      </c>
+      <c r="H38" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -1295,6 +1411,8 @@
       <c r="F39" t="n">
         <v>13</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1435,8 @@
       <c r="F40" t="n">
         <v>14</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1459,8 @@
       <c r="F41" t="n">
         <v>14</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1353,13 +1475,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="F42" t="n">
-        <v>62</v>
+        <v>23</v>
+      </c>
+      <c r="G42" t="n">
+        <v>39</v>
+      </c>
+      <c r="H42" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="43">
@@ -1375,13 +1503,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="F43" t="n">
-        <v>62</v>
+        <v>23</v>
+      </c>
+      <c r="G43" t="n">
+        <v>39</v>
+      </c>
+      <c r="H43" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -1403,8 +1537,10 @@
         <v>228</v>
       </c>
       <c r="F44" t="n">
-        <v>51</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1563,8 @@
       <c r="F45" t="n">
         <v>15</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1447,8 +1585,10 @@
         <v>316</v>
       </c>
       <c r="F46" t="n">
-        <v>29</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1611,8 @@
       <c r="F47" t="n">
         <v>20</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1635,8 @@
       <c r="F48" t="n">
         <v>18</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1659,8 @@
       <c r="F49" t="n">
         <v>13</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1683,8 @@
       <c r="F50" t="n">
         <v>14</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1707,8 @@
       <c r="F51" t="n">
         <v>14</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1731,8 @@
       <c r="F52" t="n">
         <v>31</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1755,8 @@
       <c r="F53" t="n">
         <v>32</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1617,13 +1771,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="F54" t="n">
-        <v>172</v>
+        <v>14</v>
+      </c>
+      <c r="G54" t="n">
+        <v>180</v>
+      </c>
+      <c r="H54" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -1639,13 +1799,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="F55" t="n">
-        <v>171</v>
+        <v>13</v>
+      </c>
+      <c r="G55" t="n">
+        <v>190</v>
+      </c>
+      <c r="H55" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -1661,12 +1827,18 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="F56" t="n">
+        <v>13</v>
+      </c>
+      <c r="G56" t="n">
+        <v>102</v>
+      </c>
+      <c r="H56" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1691,6 +1863,8 @@
       <c r="F57" t="n">
         <v>13</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1887,8 @@
       <c r="F58" t="n">
         <v>13</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1911,8 @@
       <c r="F59" t="n">
         <v>15</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1935,8 @@
       <c r="F60" t="n">
         <v>13</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1959,8 @@
       <c r="F61" t="n">
         <v>25</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +1983,8 @@
       <c r="F62" t="n">
         <v>25</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +2007,8 @@
       <c r="F63" t="n">
         <v>14</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1837,12 +2023,18 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="F64" t="n">
+        <v>13</v>
+      </c>
+      <c r="G64" t="n">
+        <v>89</v>
+      </c>
+      <c r="H64" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1867,6 +2059,8 @@
       <c r="F65" t="n">
         <v>13</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2083,8 @@
       <c r="F66" t="n">
         <v>23</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2107,8 @@
       <c r="F67" t="n">
         <v>13</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1925,7 +2123,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>106</v>
@@ -1933,13 +2131,19 @@
       <c r="F68" t="n">
         <v>1</v>
       </c>
+      <c r="G68" t="n">
+        <v>162</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,15 +2154,17 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B70" t="n">
         <v>11</v>
@@ -1972,18 +2178,20 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B71" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,18 +2202,20 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B72" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,33 +2226,13 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>16</v>
-      </c>
-      <c r="B73" t="n">
-        <v>23</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>185</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
